--- a/data/data_pakan_lengkap.xlsx
+++ b/data/data_pakan_lengkap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data Pakan Lengkap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Pakan Lengkap" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,627 +504,627 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Jagung Kuning Pipilan</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>8.5</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" t="n">
         <v>2.5</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>3.8</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" t="n">
         <v>3350</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>0.02</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>0.28</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" t="n">
         <v>5500</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Dedak Padi</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>3.5</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" t="n">
         <v>2800</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>0.05</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" t="n">
         <v>4200</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Sorgum</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>2.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" t="n">
         <v>3200</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>0.25</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" t="n">
         <v>4800</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Gaplek (Singkong Kering)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" t="n">
         <v>3000</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" t="n">
         <v>0.05</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" t="n">
         <v>3200</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Menir Beras</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>1.5</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" t="n">
         <v>0.05</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>0.3</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" t="n">
         <v>5500</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bungkil Kedelai (SBM)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>44</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>2250</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" t="n">
         <v>0.3</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>0.6</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" t="n">
         <v>9800</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Tepung Ikan (Lokal)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>55</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" t="n">
         <v>2900</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>2.5</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" t="n">
         <v>22000</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Tepung Daging dan Tulang (MBM)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" t="n">
         <v>2800</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" t="n">
         <v>15000</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Bungkil Kelapa (Copra Meal)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" t="n">
         <v>1900</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" t="n">
         <v>0.1</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" t="n">
         <v>7500</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Bungkil Sawit (Palm Kernel Meal)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" t="n">
         <v>1700</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" t="n">
         <v>0.15</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>0.4</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" t="n">
         <v>5800</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Ampas Tahu</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>22</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>15</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" t="n">
         <v>1500</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" t="n">
         <v>0.1</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" t="n">
         <v>0.3</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" t="n">
         <v>3500</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Pollard (Bran)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" t="n">
         <v>2800</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" t="n">
         <v>0.8</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" t="n">
         <v>4800</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Kulit Kopi Giling</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" t="n">
         <v>35</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" t="n">
         <v>0.2</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" t="n">
         <v>0.1</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" t="n">
         <v>1500</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Minyak Sawit (CPO)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>99</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" t="n">
         <v>8000</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" t="n">
         <v>12000</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Molases (Tetes Tebu)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>2800</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" t="n">
         <v>0.1</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>0.05</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" t="n">
         <v>3800</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Tepung Tulang (Steril)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>1000</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" t="n">
         <v>20</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>10</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" t="n">
         <v>6500</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Garam Dapur Beryodium</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" t="n">
         <v>5000</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Premix Ayam Pedaging</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" t="n">
         <v>35</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" t="n">
         <v>2500</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" t="n">
         <v>25000</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Premix Ayam Petelur</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>40</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>7</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" t="n">
         <v>2400</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" t="n">
         <v>30000</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Referensi Industri</t>
         </is>
